--- a/artfynd/Rislidtjärnarna artfynd.xlsx
+++ b/artfynd/Rislidtjärnarna artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY190"/>
+  <dimension ref="A1:AY191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7940,7 +7940,7 @@
         <v>126905648</v>
       </c>
       <c r="B72" t="n">
-        <v>57839</v>
+        <v>57860</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8388,45 +8388,57 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126919980</v>
+        <v>126919961</v>
       </c>
       <c r="B76" t="n">
-        <v>41601</v>
+        <v>58131</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>215713</v>
+        <v>103023</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Grå blåbärsfältmätare</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Entephria caesiata</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Rislidstjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>688404</v>
+        <v>688452</v>
       </c>
       <c r="R76" t="n">
-        <v>7098538</v>
+        <v>7098454</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8467,7 +8479,6 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8490,49 +8501,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126917650</v>
+        <v>126919980</v>
       </c>
       <c r="B77" t="n">
-        <v>99140</v>
+        <v>41601</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>221952</v>
+        <v>215713</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Grå blåbärsfältmätare</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Entephria caesiata</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Kåtabäcken, Ång</t>
+          <t>Rislidstjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>688477</v>
+        <v>688404</v>
       </c>
       <c r="R77" t="n">
-        <v>7098528</v>
+        <v>7098538</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8580,12 +8587,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Malin Löfgren, Isac Enetjärn, Nicklas Gustavsson, Fredrik Wilde, Eleonor Johansson, Lotta Ihse, Hedda Bring, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
@@ -8596,45 +8603,49 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126917548</v>
+        <v>126917650</v>
       </c>
       <c r="B78" t="n">
-        <v>79085</v>
+        <v>99140</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>228912</v>
+        <v>221952</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Rislidtjärnarna, Ång</t>
+          <t>Kåtabäcken, Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>688397</v>
+        <v>688477</v>
       </c>
       <c r="R78" t="n">
-        <v>7098418</v>
+        <v>7098528</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8675,18 +8686,19 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -8697,10 +8709,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126918463</v>
+        <v>126917548</v>
       </c>
       <c r="B79" t="n">
-        <v>97358</v>
+        <v>79085</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8708,38 +8720,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>53</v>
+        <v>228912</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>S Rislidsmyran, Ång</t>
+          <t>Rislidtjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>689364</v>
+        <v>688397</v>
       </c>
       <c r="R79" t="n">
-        <v>7098209</v>
+        <v>7098418</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8780,19 +8788,18 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -8803,7 +8810,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126919957</v>
+        <v>126918463</v>
       </c>
       <c r="B80" t="n">
         <v>97358</v>
@@ -8832,16 +8839,20 @@
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Rislidstjärnarna, Ång</t>
+          <t>S Rislidsmyran, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>689375</v>
+        <v>689364</v>
       </c>
       <c r="R80" t="n">
-        <v>7098205</v>
+        <v>7098209</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8882,18 +8893,19 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Malin Löfgren, Isac Enetjärn, Nicklas Gustavsson, Fredrik Wilde, Eleonor Johansson, Lotta Ihse, Hedda Bring, Emil Lindgren</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -8904,10 +8916,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126918491</v>
+        <v>126919957</v>
       </c>
       <c r="B81" t="n">
-        <v>91909</v>
+        <v>97358</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8915,37 +8927,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>S Rislidsmyran, Ång</t>
+          <t>Rislidstjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>689317</v>
+        <v>689375</v>
       </c>
       <c r="R81" t="n">
-        <v>7098192</v>
+        <v>7098205</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8986,19 +8995,18 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Malin Löfgren, Isac Enetjärn, Nicklas Gustavsson, Fredrik Wilde, Eleonor Johansson, Lotta Ihse, Hedda Bring, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
@@ -9009,7 +9017,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126919984</v>
+        <v>126918491</v>
       </c>
       <c r="B82" t="n">
         <v>91909</v>
@@ -9038,16 +9046,19 @@
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Rislidstjärnarna, Ång</t>
+          <t>S Rislidsmyran, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>689272</v>
+        <v>689317</v>
       </c>
       <c r="R82" t="n">
-        <v>7098206</v>
+        <v>7098192</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9088,18 +9099,19 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Malin Löfgren, Isac Enetjärn, Nicklas Gustavsson, Fredrik Wilde, Eleonor Johansson, Lotta Ihse, Hedda Bring, Emil Lindgren</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -9110,10 +9122,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>56825848</v>
+        <v>126919984</v>
       </c>
       <c r="B83" t="n">
-        <v>83173</v>
+        <v>91909</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9121,34 +9133,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Rislidtjärnarna, Ång</t>
+          <t>Rislidstjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>689391</v>
+        <v>689272</v>
       </c>
       <c r="R83" t="n">
-        <v>7098147</v>
+        <v>7098206</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9175,12 +9187,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2015-05-18</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2015-10-30</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9191,83 +9203,65 @@
       </c>
       <c r="AG83" t="b">
         <v>0</v>
-      </c>
-      <c r="AI83" t="inlineStr">
-        <is>
-          <t>barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AO83" t="inlineStr">
-        <is>
-          <t>gammal gran</t>
-        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY83" t="inlineStr"/>
+          <t>Malin Löfgren, Isac Enetjärn, Nicklas Gustavsson, Fredrik Wilde, Eleonor Johansson, Lotta Ihse, Hedda Bring, Emil Lindgren</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126911379</v>
+        <v>56825848</v>
       </c>
       <c r="B84" t="n">
-        <v>57141</v>
+        <v>83173</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100138</v>
+        <v>1312</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>rastande</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Rislidtjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>689283</v>
+        <v>689391</v>
       </c>
       <c r="R84" t="n">
-        <v>7098261</v>
+        <v>7098147</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9294,22 +9288,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>2015-05-18</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>2015-10-30</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9320,30 +9304,36 @@
       </c>
       <c r="AG84" t="b">
         <v>0</v>
+      </c>
+      <c r="AI84" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO84" t="inlineStr">
+        <is>
+          <t>gammal gran</t>
+        </is>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
-        </is>
-      </c>
-      <c r="AY84" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126919996</v>
+        <v>126911379</v>
       </c>
       <c r="B85" t="n">
-        <v>99035</v>
+        <v>57141</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9351,34 +9341,46 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>219790</v>
+        <v>100138</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Rislidstjärnarna, Ång</t>
+          <t>Rislidtjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>689260</v>
+        <v>689283</v>
       </c>
       <c r="R85" t="n">
-        <v>7098185</v>
+        <v>7098261</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9408,9 +9410,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9425,12 +9437,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Malin Löfgren, Isac Enetjärn, Nicklas Gustavsson, Fredrik Wilde, Eleonor Johansson, Lotta Ihse, Hedda Bring, Emil Lindgren</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
@@ -9441,48 +9453,45 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126918232</v>
+        <v>126919996</v>
       </c>
       <c r="B86" t="n">
-        <v>91909</v>
+        <v>99035</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1202</v>
+        <v>219790</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>V Rislidsmyran, Ång</t>
+          <t>Rislidstjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>688834</v>
+        <v>689260</v>
       </c>
       <c r="R86" t="n">
-        <v>7098482</v>
+        <v>7098185</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9523,19 +9532,18 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Malin Löfgren, Isac Enetjärn, Nicklas Gustavsson, Fredrik Wilde, Eleonor Johansson, Lotta Ihse, Hedda Bring, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
@@ -9546,45 +9554,48 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126915428</v>
+        <v>126918232</v>
       </c>
       <c r="B87" t="n">
-        <v>91923</v>
+        <v>91909</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Rislidtjärnarna, Ång</t>
+          <t>V Rislidsmyran, Ång</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>688926</v>
+        <v>688834</v>
       </c>
       <c r="R87" t="n">
-        <v>7098451</v>
+        <v>7098482</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9625,18 +9636,19 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Hedda Bring, Eleonor Johansson, Emil Lindgren, Fredrik Wilde, Isac Enetjärn, Lotta Ihse, Malin Löfgren, Eleonor Johansson, Emil Lindgren, Fredrik Wilde, Isac Enetjärn, Lotta Ihse, Malin Löfgren</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
@@ -9647,7 +9659,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126919982</v>
+        <v>126915428</v>
       </c>
       <c r="B88" t="n">
         <v>91923</v>
@@ -9678,11 +9690,11 @@
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Rislidstjärnarna, Ång</t>
+          <t>Rislidtjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>688925</v>
+        <v>688926</v>
       </c>
       <c r="R88" t="n">
         <v>7098451</v>
@@ -9732,12 +9744,12 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Malin Löfgren, Isac Enetjärn, Nicklas Gustavsson, Fredrik Wilde, Eleonor Johansson, Lotta Ihse, Hedda Bring, Emil Lindgren</t>
+          <t>Hedda Bring, Eleonor Johansson, Emil Lindgren, Fredrik Wilde, Isac Enetjärn, Lotta Ihse, Malin Löfgren, Eleonor Johansson, Emil Lindgren, Fredrik Wilde, Isac Enetjärn, Lotta Ihse, Malin Löfgren</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
@@ -9748,45 +9760,45 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126907339</v>
+        <v>126919982</v>
       </c>
       <c r="B89" t="n">
-        <v>83173</v>
+        <v>91923</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Rislidmyran, Rislidmyran, Ång</t>
+          <t>Rislidstjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>688902</v>
+        <v>688925</v>
       </c>
       <c r="R89" t="n">
-        <v>7098449</v>
+        <v>7098451</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9816,19 +9828,9 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>13:05</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9843,12 +9845,12 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Eleonor Johansson</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Eleonor Johansson, Lotta Ihse, Isac Enetjärn, Fredrik Wilde, Malin Löfgren, Emil Lindgren, Hedda Bring</t>
+          <t>Malin Löfgren, Isac Enetjärn, Nicklas Gustavsson, Fredrik Wilde, Eleonor Johansson, Lotta Ihse, Hedda Bring, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
@@ -9859,7 +9861,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126918261</v>
+        <v>126907339</v>
       </c>
       <c r="B90" t="n">
         <v>83173</v>
@@ -9888,19 +9890,16 @@
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>V Rislidsmyran, Ång</t>
+          <t>Rislidmyran, Rislidmyran, Ång</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>689016</v>
+        <v>688902</v>
       </c>
       <c r="R90" t="n">
-        <v>7098469</v>
+        <v>7098449</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9930,30 +9929,39 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AD90" t="b">
         <v>0</v>
       </c>
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Eleonor Johansson</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Eleonor Johansson, Lotta Ihse, Isac Enetjärn, Fredrik Wilde, Malin Löfgren, Emil Lindgren, Hedda Bring</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
@@ -9964,7 +9972,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126919991</v>
+        <v>126918261</v>
       </c>
       <c r="B91" t="n">
         <v>83173</v>
@@ -9993,16 +10001,19 @@
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Rislidstjärnarna, Ång</t>
+          <t>V Rislidsmyran, Ång</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>689024</v>
+        <v>689016</v>
       </c>
       <c r="R91" t="n">
-        <v>7098471</v>
+        <v>7098469</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10043,18 +10054,19 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Malin Löfgren, Isac Enetjärn, Nicklas Gustavsson, Fredrik Wilde, Eleonor Johansson, Lotta Ihse, Hedda Bring, Emil Lindgren</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
@@ -10065,7 +10077,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126919993</v>
+        <v>126919991</v>
       </c>
       <c r="B92" t="n">
         <v>83173</v>
@@ -10100,10 +10112,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>688851</v>
+        <v>689024</v>
       </c>
       <c r="R92" t="n">
-        <v>7098465</v>
+        <v>7098471</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10144,7 +10156,6 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -10167,45 +10178,45 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126907558</v>
+        <v>126919993</v>
       </c>
       <c r="B93" t="n">
-        <v>91872</v>
+        <v>83173</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Rislidmyran, Rislidmyran, Ång</t>
+          <t>Rislidstjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>688962</v>
+        <v>688851</v>
       </c>
       <c r="R93" t="n">
-        <v>7098446</v>
+        <v>7098465</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10235,39 +10246,30 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
       <c r="AD93" t="b">
         <v>0</v>
       </c>
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Eleonor Johansson</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Eleonor Johansson, Lotta Ihse, Isac Enetjärn, Fredrik Wilde, Malin Löfgren, Emil Lindgren, Hedda Bring</t>
+          <t>Malin Löfgren, Isac Enetjärn, Nicklas Gustavsson, Fredrik Wilde, Eleonor Johansson, Lotta Ihse, Hedda Bring, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
@@ -10278,7 +10280,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126915422</v>
+        <v>126907558</v>
       </c>
       <c r="B94" t="n">
         <v>91872</v>
@@ -10309,14 +10311,14 @@
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Rislidtjärnarna, Ång</t>
+          <t>Rislidmyran, Rislidmyran, Ång</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>688928</v>
+        <v>688962</v>
       </c>
       <c r="R94" t="n">
-        <v>7098449</v>
+        <v>7098446</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10346,9 +10348,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10363,12 +10375,12 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Eleonor Johansson</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Hedda Bring, Eleonor Johansson, Emil Lindgren, Fredrik Wilde, Isac Enetjärn, Lotta Ihse, Malin Löfgren, Eleonor Johansson, Emil Lindgren, Fredrik Wilde, Isac Enetjärn, Lotta Ihse, Malin Löfgren</t>
+          <t>Eleonor Johansson, Lotta Ihse, Isac Enetjärn, Fredrik Wilde, Malin Löfgren, Emil Lindgren, Hedda Bring</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
@@ -10379,7 +10391,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126918241</v>
+        <v>126915422</v>
       </c>
       <c r="B95" t="n">
         <v>91872</v>
@@ -10408,19 +10420,16 @@
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>V Rislidsmyran, Ång</t>
+          <t>Rislidtjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>688851</v>
+        <v>688928</v>
       </c>
       <c r="R95" t="n">
-        <v>7098466</v>
+        <v>7098449</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10461,19 +10470,18 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Hedda Bring, Eleonor Johansson, Emil Lindgren, Fredrik Wilde, Isac Enetjärn, Lotta Ihse, Malin Löfgren, Eleonor Johansson, Emil Lindgren, Fredrik Wilde, Isac Enetjärn, Lotta Ihse, Malin Löfgren</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
@@ -10484,7 +10492,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126919958</v>
+        <v>126918241</v>
       </c>
       <c r="B96" t="n">
         <v>91872</v>
@@ -10513,16 +10521,19 @@
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Rislidstjärnarna, Ång</t>
+          <t>V Rislidsmyran, Ång</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>688962</v>
+        <v>688851</v>
       </c>
       <c r="R96" t="n">
-        <v>7098452</v>
+        <v>7098466</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10563,18 +10574,19 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Malin Löfgren, Isac Enetjärn, Nicklas Gustavsson, Fredrik Wilde, Eleonor Johansson, Lotta Ihse, Hedda Bring, Emil Lindgren</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
@@ -10585,7 +10597,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126919959</v>
+        <v>126919958</v>
       </c>
       <c r="B97" t="n">
         <v>91872</v>
@@ -10620,10 +10632,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>688929</v>
+        <v>688962</v>
       </c>
       <c r="R97" t="n">
-        <v>7098453</v>
+        <v>7098452</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10686,50 +10698,45 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126907670</v>
+        <v>126919959</v>
       </c>
       <c r="B98" t="n">
-        <v>79327</v>
+        <v>91872</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Rislidmyran, Rislidmyran, Ång</t>
+          <t>Rislidstjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>688977</v>
+        <v>688929</v>
       </c>
       <c r="R98" t="n">
-        <v>7098450</v>
+        <v>7098453</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10759,19 +10766,9 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z98" t="inlineStr">
-        <is>
-          <t>13:24</t>
-        </is>
-      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB98" t="inlineStr">
-        <is>
-          <t>13:24</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10786,12 +10783,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Eleonor Johansson</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Eleonor Johansson, Lotta Ihse, Isac Enetjärn, Fredrik Wilde, Malin Löfgren, Emil Lindgren, Hedda Bring</t>
+          <t>Malin Löfgren, Isac Enetjärn, Nicklas Gustavsson, Fredrik Wilde, Eleonor Johansson, Lotta Ihse, Hedda Bring, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -10802,7 +10799,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126911318</v>
+        <v>126907670</v>
       </c>
       <c r="B99" t="n">
         <v>79327</v>
@@ -10831,19 +10828,21 @@
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Rislidtjärnarna, Ång</t>
+          <t>Rislidmyran, Rislidmyran, Ång</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>688836</v>
+        <v>688977</v>
       </c>
       <c r="R99" t="n">
-        <v>7098618</v>
+        <v>7098450</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10873,30 +10872,39 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
       <c r="AD99" t="b">
         <v>0</v>
       </c>
       <c r="AE99" t="b">
         <v>0</v>
       </c>
-      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Eleonor Johansson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Eleonor Johansson, Lotta Ihse, Isac Enetjärn, Fredrik Wilde, Malin Löfgren, Emil Lindgren, Hedda Bring</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -10907,7 +10915,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126915430</v>
+        <v>126911318</v>
       </c>
       <c r="B100" t="n">
         <v>79327</v>
@@ -10936,16 +10944,19 @@
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Rislidtjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>689029</v>
+        <v>688836</v>
       </c>
       <c r="R100" t="n">
-        <v>7098478</v>
+        <v>7098618</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10986,18 +10997,19 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Hedda Bring, Eleonor Johansson, Emil Lindgren, Fredrik Wilde, Isac Enetjärn, Lotta Ihse, Malin Löfgren, Eleonor Johansson, Emil Lindgren, Fredrik Wilde, Isac Enetjärn, Lotta Ihse, Malin Löfgren</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -11008,7 +11020,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126915431</v>
+        <v>126915430</v>
       </c>
       <c r="B101" t="n">
         <v>79327</v>
@@ -11043,10 +11055,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>688868</v>
+        <v>689029</v>
       </c>
       <c r="R101" t="n">
-        <v>7098462</v>
+        <v>7098478</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11109,7 +11121,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>126915735</v>
+        <v>126915431</v>
       </c>
       <c r="B102" t="n">
         <v>79327</v>
@@ -11144,10 +11156,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>689201</v>
+        <v>688868</v>
       </c>
       <c r="R102" t="n">
-        <v>7098545</v>
+        <v>7098462</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11194,12 +11206,12 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Lotta Ihse, Hedda Bring, Fredrik Wilde, Eleonor Johansson, Malin Löfgren, Emil Lindgren, Isac Enetjärn</t>
+          <t>Hedda Bring, Eleonor Johansson, Emil Lindgren, Fredrik Wilde, Isac Enetjärn, Lotta Ihse, Malin Löfgren, Eleonor Johansson, Emil Lindgren, Fredrik Wilde, Isac Enetjärn, Lotta Ihse, Malin Löfgren</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
@@ -11210,7 +11222,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>126915736</v>
+        <v>126915735</v>
       </c>
       <c r="B103" t="n">
         <v>79327</v>
@@ -11245,10 +11257,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>689058</v>
+        <v>689201</v>
       </c>
       <c r="R103" t="n">
-        <v>7098484</v>
+        <v>7098545</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11311,7 +11323,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>126915737</v>
+        <v>126915736</v>
       </c>
       <c r="B104" t="n">
         <v>79327</v>
@@ -11346,10 +11358,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>688970</v>
+        <v>689058</v>
       </c>
       <c r="R104" t="n">
-        <v>7098460</v>
+        <v>7098484</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11412,7 +11424,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>126915738</v>
+        <v>126915737</v>
       </c>
       <c r="B105" t="n">
         <v>79327</v>
@@ -11447,10 +11459,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>688853</v>
+        <v>688970</v>
       </c>
       <c r="R105" t="n">
-        <v>7098469</v>
+        <v>7098460</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11513,7 +11525,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126915740</v>
+        <v>126915738</v>
       </c>
       <c r="B106" t="n">
         <v>79327</v>
@@ -11548,10 +11560,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>689096</v>
+        <v>688853</v>
       </c>
       <c r="R106" t="n">
-        <v>7098533</v>
+        <v>7098469</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11614,7 +11626,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126915741</v>
+        <v>126915740</v>
       </c>
       <c r="B107" t="n">
         <v>79327</v>
@@ -11649,10 +11661,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>689051</v>
+        <v>689096</v>
       </c>
       <c r="R107" t="n">
-        <v>7098484</v>
+        <v>7098533</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11715,7 +11727,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>126917559</v>
+        <v>126915741</v>
       </c>
       <c r="B108" t="n">
         <v>79327</v>
@@ -11750,10 +11762,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>688945</v>
+        <v>689051</v>
       </c>
       <c r="R108" t="n">
-        <v>7098719</v>
+        <v>7098484</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11788,30 +11800,24 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>Rikligt på tallstammar</t>
-        </is>
-      </c>
       <c r="AD108" t="b">
         <v>0</v>
       </c>
       <c r="AE108" t="b">
         <v>0</v>
       </c>
-      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Lotta Ihse, Hedda Bring, Fredrik Wilde, Eleonor Johansson, Malin Löfgren, Emil Lindgren, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
@@ -11822,7 +11828,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>126917560</v>
+        <v>126917559</v>
       </c>
       <c r="B109" t="n">
         <v>79327</v>
@@ -11857,10 +11863,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>688956</v>
+        <v>688945</v>
       </c>
       <c r="R109" t="n">
-        <v>7098761</v>
+        <v>7098719</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11897,7 +11903,7 @@
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>Mkt garnlavsrikt i närområdet</t>
+          <t>Rikligt på tallstammar</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11929,7 +11935,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>126917561</v>
+        <v>126917560</v>
       </c>
       <c r="B110" t="n">
         <v>79327</v>
@@ -11964,10 +11970,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>688869</v>
+        <v>688956</v>
       </c>
       <c r="R110" t="n">
-        <v>7098679</v>
+        <v>7098761</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12002,12 +12008,18 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>Mkt garnlavsrikt i närområdet</t>
+        </is>
+      </c>
       <c r="AD110" t="b">
         <v>0</v>
       </c>
       <c r="AE110" t="b">
         <v>0</v>
       </c>
+      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
@@ -12030,7 +12042,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>126917564</v>
+        <v>126917561</v>
       </c>
       <c r="B111" t="n">
         <v>79327</v>
@@ -12065,10 +12077,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>688884</v>
+        <v>688869</v>
       </c>
       <c r="R111" t="n">
-        <v>7098789</v>
+        <v>7098679</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12131,7 +12143,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>126918250</v>
+        <v>126917564</v>
       </c>
       <c r="B112" t="n">
         <v>79327</v>
@@ -12160,19 +12172,16 @@
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="J112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
-      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>V Rislidsmyran, Ång</t>
+          <t>Rislidtjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>688908</v>
+        <v>688884</v>
       </c>
       <c r="R112" t="n">
-        <v>7098461</v>
+        <v>7098789</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12213,19 +12222,18 @@
       <c r="AE112" t="b">
         <v>0</v>
       </c>
-      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
       </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
@@ -12236,7 +12244,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>126919987</v>
+        <v>126918250</v>
       </c>
       <c r="B113" t="n">
         <v>79327</v>
@@ -12265,16 +12273,19 @@
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Rislidstjärnarna, Ång</t>
+          <t>V Rislidsmyran, Ång</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>689137</v>
+        <v>688908</v>
       </c>
       <c r="R113" t="n">
-        <v>7098549</v>
+        <v>7098461</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12315,18 +12326,19 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
+      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Malin Löfgren, Isac Enetjärn, Nicklas Gustavsson, Fredrik Wilde, Eleonor Johansson, Lotta Ihse, Hedda Bring, Emil Lindgren</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
@@ -12337,45 +12349,45 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126907346</v>
+        <v>126919987</v>
       </c>
       <c r="B114" t="n">
-        <v>83307</v>
+        <v>79327</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Rislidmyran, Rislidmyran, Ång</t>
+          <t>Rislidstjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>688894</v>
+        <v>689137</v>
       </c>
       <c r="R114" t="n">
-        <v>7098446</v>
+        <v>7098549</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12405,19 +12417,9 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z114" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB114" t="inlineStr">
-        <is>
-          <t>13:05</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12432,12 +12434,12 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Eleonor Johansson</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Eleonor Johansson, Lotta Ihse, Isac Enetjärn, Fredrik Wilde, Malin Löfgren, Emil Lindgren, Hedda Bring</t>
+          <t>Malin Löfgren, Isac Enetjärn, Nicklas Gustavsson, Fredrik Wilde, Eleonor Johansson, Lotta Ihse, Hedda Bring, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
@@ -12448,7 +12450,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>126917527</v>
+        <v>126907346</v>
       </c>
       <c r="B115" t="n">
         <v>83307</v>
@@ -12479,14 +12481,14 @@
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Rislidtjärnarna, Ång</t>
+          <t>Rislidmyran, Rislidmyran, Ång</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>689012</v>
+        <v>688894</v>
       </c>
       <c r="R115" t="n">
-        <v>7098665</v>
+        <v>7098446</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12516,9 +12518,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12533,12 +12545,12 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Eleonor Johansson</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Eleonor Johansson, Lotta Ihse, Isac Enetjärn, Fredrik Wilde, Malin Löfgren, Emil Lindgren, Hedda Bring</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
@@ -12549,7 +12561,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>126919950</v>
+        <v>126917527</v>
       </c>
       <c r="B116" t="n">
         <v>83307</v>
@@ -12580,14 +12592,14 @@
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Rislidstjärnarna, Ång</t>
+          <t>Rislidtjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>689067</v>
+        <v>689012</v>
       </c>
       <c r="R116" t="n">
-        <v>7098482</v>
+        <v>7098665</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12634,12 +12646,12 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Malin Löfgren, Isac Enetjärn, Nicklas Gustavsson, Fredrik Wilde, Eleonor Johansson, Lotta Ihse, Hedda Bring, Emil Lindgren</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
@@ -12650,48 +12662,45 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>126918388</v>
+        <v>126919950</v>
       </c>
       <c r="B117" t="n">
-        <v>80336</v>
+        <v>83307</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6456</v>
+        <v>6440</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
-      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>V Rislidsmyran, Ång</t>
+          <t>Rislidstjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>689074</v>
+        <v>689067</v>
       </c>
       <c r="R117" t="n">
-        <v>7098504</v>
+        <v>7098482</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12732,19 +12741,18 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
-      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Malin Löfgren, Isac Enetjärn, Nicklas Gustavsson, Fredrik Wilde, Eleonor Johansson, Lotta Ihse, Hedda Bring, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
@@ -12755,7 +12763,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>126919969</v>
+        <v>126918388</v>
       </c>
       <c r="B118" t="n">
         <v>80336</v>
@@ -12784,16 +12792,19 @@
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Rislidstjärnarna, Ång</t>
+          <t>V Rislidsmyran, Ång</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>689071</v>
+        <v>689074</v>
       </c>
       <c r="R118" t="n">
-        <v>7098498</v>
+        <v>7098504</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12834,18 +12845,19 @@
       <c r="AE118" t="b">
         <v>0</v>
       </c>
+      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Malin Löfgren, Isac Enetjärn, Nicklas Gustavsson, Fredrik Wilde, Eleonor Johansson, Lotta Ihse, Hedda Bring, Emil Lindgren</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
@@ -12856,10 +12868,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>126917541</v>
+        <v>126919969</v>
       </c>
       <c r="B119" t="n">
-        <v>57950</v>
+        <v>80336</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12867,38 +12879,34 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100049</v>
+        <v>6456</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="K119" t="inlineStr"/>
-      <c r="L119" t="inlineStr"/>
-      <c r="M119" t="inlineStr"/>
-      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Rislidtjärnarna, Ång</t>
+          <t>Rislidstjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>688875</v>
+        <v>689071</v>
       </c>
       <c r="R119" t="n">
-        <v>7098694</v>
+        <v>7098498</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12933,11 +12941,6 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>Ädre spår</t>
-        </is>
-      </c>
       <c r="AD119" t="b">
         <v>0</v>
       </c>
@@ -12950,12 +12953,12 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Malin Löfgren, Isac Enetjärn, Nicklas Gustavsson, Fredrik Wilde, Eleonor Johansson, Lotta Ihse, Hedda Bring, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr">
@@ -12966,10 +12969,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>126911337</v>
+        <v>126917541</v>
       </c>
       <c r="B120" t="n">
-        <v>5179</v>
+        <v>57950</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12977,32 +12980,27 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr"/>
       <c r="L120" t="inlineStr"/>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M120" t="inlineStr"/>
       <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
@@ -13010,10 +13008,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>688887</v>
+        <v>688875</v>
       </c>
       <c r="R120" t="n">
-        <v>7098710</v>
+        <v>7098694</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13048,25 +13046,29 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>Ädre spår</t>
+        </is>
+      </c>
       <c r="AD120" t="b">
         <v>0</v>
       </c>
       <c r="AE120" t="b">
         <v>0</v>
       </c>
-      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr">
@@ -13077,45 +13079,54 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>126917536</v>
+        <v>126911337</v>
       </c>
       <c r="B121" t="n">
-        <v>58114</v>
+        <v>5179</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>103021</v>
+        <v>100526</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Rislidtjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>689179</v>
+        <v>688887</v>
       </c>
       <c r="R121" t="n">
-        <v>7098544</v>
+        <v>7098710</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13150,29 +13161,25 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>Bohål i murken tallhögstubbe. Troligen talltita</t>
-        </is>
-      </c>
       <c r="AD121" t="b">
         <v>0</v>
       </c>
       <c r="AE121" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
@@ -13183,7 +13190,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>126917537</v>
+        <v>126917536</v>
       </c>
       <c r="B122" t="n">
         <v>58114</v>
@@ -13218,10 +13225,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>689016</v>
+        <v>689179</v>
       </c>
       <c r="R122" t="n">
-        <v>7098681</v>
+        <v>7098544</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13256,11 +13263,16 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>Bohål i murken tallhögstubbe. Troligen talltita</t>
+        </is>
+      </c>
       <c r="AD122" t="b">
         <v>0</v>
       </c>
       <c r="AE122" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG122" t="b">
         <v>0</v>
@@ -13284,10 +13296,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>126915426</v>
+        <v>126917537</v>
       </c>
       <c r="B123" t="n">
-        <v>58057</v>
+        <v>58114</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13295,42 +13307,34 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>103031</v>
+        <v>103021</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K123" t="inlineStr"/>
-      <c r="L123" t="inlineStr"/>
-      <c r="M123" t="inlineStr"/>
-      <c r="N123" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Rislidtjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>689107</v>
+        <v>689016</v>
       </c>
       <c r="R123" t="n">
-        <v>7098552</v>
+        <v>7098681</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13377,12 +13381,12 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Hedda Bring, Eleonor Johansson, Emil Lindgren, Fredrik Wilde, Isac Enetjärn, Lotta Ihse, Malin Löfgren, Eleonor Johansson, Emil Lindgren, Fredrik Wilde, Isac Enetjärn, Lotta Ihse, Malin Löfgren</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr">
@@ -13393,7 +13397,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>126919973</v>
+        <v>126915426</v>
       </c>
       <c r="B124" t="n">
         <v>58057</v>
@@ -13426,28 +13430,20 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr">
-        <is>
-          <t>1K</t>
-        </is>
-      </c>
+      <c r="K124" t="inlineStr"/>
       <c r="L124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+      <c r="M124" t="inlineStr"/>
       <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Rislidstjärnarna, Ång</t>
+          <t>Rislidtjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>689106</v>
+        <v>689107</v>
       </c>
       <c r="R124" t="n">
-        <v>7098548</v>
+        <v>7098552</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13494,12 +13490,12 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Malin Löfgren, Isac Enetjärn, Nicklas Gustavsson, Fredrik Wilde, Eleonor Johansson, Lotta Ihse, Hedda Bring, Emil Lindgren</t>
+          <t>Hedda Bring, Eleonor Johansson, Emil Lindgren, Fredrik Wilde, Isac Enetjärn, Lotta Ihse, Malin Löfgren, Eleonor Johansson, Emil Lindgren, Fredrik Wilde, Isac Enetjärn, Lotta Ihse, Malin Löfgren</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr">
@@ -13510,10 +13506,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>126917538</v>
+        <v>126919973</v>
       </c>
       <c r="B125" t="n">
-        <v>79350</v>
+        <v>58057</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13521,34 +13517,50 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>260591</v>
+        <v>103031</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Rislidtjärnarna, Ång</t>
+          <t>Rislidstjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>689139</v>
+        <v>689106</v>
       </c>
       <c r="R125" t="n">
-        <v>7098547</v>
+        <v>7098548</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13595,12 +13607,12 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Malin Löfgren, Isac Enetjärn, Nicklas Gustavsson, Fredrik Wilde, Eleonor Johansson, Lotta Ihse, Hedda Bring, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
@@ -13611,7 +13623,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>126919963</v>
+        <v>126917538</v>
       </c>
       <c r="B126" t="n">
         <v>79350</v>
@@ -13642,14 +13654,14 @@
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Rislidstjärnarna, Ång</t>
+          <t>Rislidtjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>689107</v>
+        <v>689139</v>
       </c>
       <c r="R126" t="n">
-        <v>7098546</v>
+        <v>7098547</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13696,12 +13708,12 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Malin Löfgren, Isac Enetjärn, Nicklas Gustavsson, Fredrik Wilde, Eleonor Johansson, Lotta Ihse, Hedda Bring, Emil Lindgren</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr">
@@ -13712,10 +13724,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>56825831</v>
+        <v>126919963</v>
       </c>
       <c r="B127" t="n">
-        <v>79359</v>
+        <v>79350</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13723,34 +13735,34 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>185</v>
+        <v>260591</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Rislidtjärnarna, Ång</t>
+          <t>Rislidstjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>689929</v>
+        <v>689107</v>
       </c>
       <c r="R127" t="n">
-        <v>7098189</v>
+        <v>7098546</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13777,12 +13789,12 @@
       </c>
       <c r="Y127" t="inlineStr">
         <is>
-          <t>2015-05-18</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2015-10-30</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13793,36 +13805,30 @@
       </c>
       <c r="AG127" t="b">
         <v>0</v>
-      </c>
-      <c r="AI127" t="inlineStr">
-        <is>
-          <t>barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AO127" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
       </c>
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY127" t="inlineStr"/>
+          <t>Malin Löfgren, Isac Enetjärn, Nicklas Gustavsson, Fredrik Wilde, Eleonor Johansson, Lotta Ihse, Hedda Bring, Emil Lindgren</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>56825846</v>
+        <v>56825831</v>
       </c>
       <c r="B128" t="n">
-        <v>91909</v>
+        <v>79359</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13830,21 +13836,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13854,10 +13860,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>689498</v>
+        <v>689929</v>
       </c>
       <c r="R128" t="n">
-        <v>7098114</v>
+        <v>7098189</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13908,7 +13914,7 @@
       </c>
       <c r="AO128" t="inlineStr">
         <is>
-          <t>granlåga</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AT128" t="inlineStr"/>
@@ -13926,7 +13932,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>126917532</v>
+        <v>56825846</v>
       </c>
       <c r="B129" t="n">
         <v>91909</v>
@@ -13961,10 +13967,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>689495</v>
+        <v>689498</v>
       </c>
       <c r="R129" t="n">
-        <v>7098044</v>
+        <v>7098114</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13991,12 +13997,12 @@
       </c>
       <c r="Y129" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2015-05-18</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2015-10-30</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14007,30 +14013,36 @@
       </c>
       <c r="AG129" t="b">
         <v>0</v>
+      </c>
+      <c r="AI129" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO129" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
       </c>
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
-        </is>
-      </c>
-      <c r="AY129" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>56825833</v>
+        <v>126917532</v>
       </c>
       <c r="B130" t="n">
-        <v>83173</v>
+        <v>91909</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14038,21 +14050,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14062,10 +14074,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>689911</v>
+        <v>689495</v>
       </c>
       <c r="R130" t="n">
-        <v>7098152</v>
+        <v>7098044</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14092,12 +14104,12 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2015-05-18</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2015-10-30</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14108,33 +14120,27 @@
       </c>
       <c r="AG130" t="b">
         <v>0</v>
-      </c>
-      <c r="AI130" t="inlineStr">
-        <is>
-          <t>barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AO130" t="inlineStr">
-        <is>
-          <t>gammal gran</t>
-        </is>
       </c>
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY130" t="inlineStr"/>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY130" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>56825834</v>
+        <v>56825833</v>
       </c>
       <c r="B131" t="n">
         <v>83173</v>
@@ -14169,10 +14175,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>689889</v>
+        <v>689911</v>
       </c>
       <c r="R131" t="n">
-        <v>7098165</v>
+        <v>7098152</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14241,7 +14247,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>56825842</v>
+        <v>56825834</v>
       </c>
       <c r="B132" t="n">
         <v>83173</v>
@@ -14276,10 +14282,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>689480</v>
+        <v>689889</v>
       </c>
       <c r="R132" t="n">
-        <v>7098098</v>
+        <v>7098165</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14348,7 +14354,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>56825844</v>
+        <v>56825842</v>
       </c>
       <c r="B133" t="n">
         <v>83173</v>
@@ -14383,7 +14389,7 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>689498</v>
+        <v>689480</v>
       </c>
       <c r="R133" t="n">
         <v>7098098</v>
@@ -14455,7 +14461,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>56825845</v>
+        <v>56825844</v>
       </c>
       <c r="B134" t="n">
         <v>83173</v>
@@ -14490,10 +14496,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>689497</v>
+        <v>689498</v>
       </c>
       <c r="R134" t="n">
-        <v>7098095</v>
+        <v>7098098</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14562,7 +14568,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>56825847</v>
+        <v>56825845</v>
       </c>
       <c r="B135" t="n">
         <v>83173</v>
@@ -14597,10 +14603,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>689415</v>
+        <v>689497</v>
       </c>
       <c r="R135" t="n">
-        <v>7098168</v>
+        <v>7098095</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14669,32 +14675,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>126917531</v>
+        <v>56825847</v>
       </c>
       <c r="B136" t="n">
-        <v>92281</v>
+        <v>83173</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>2062</v>
+        <v>1312</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14704,10 +14710,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>689506</v>
+        <v>689415</v>
       </c>
       <c r="R136" t="n">
-        <v>7098051</v>
+        <v>7098168</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14734,12 +14740,12 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2015-05-18</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2015-10-30</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14750,30 +14756,36 @@
       </c>
       <c r="AG136" t="b">
         <v>0</v>
+      </c>
+      <c r="AI136" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO136" t="inlineStr">
+        <is>
+          <t>gammal gran</t>
+        </is>
       </c>
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
-        </is>
-      </c>
-      <c r="AY136" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>56825832</v>
+        <v>126917531</v>
       </c>
       <c r="B137" t="n">
-        <v>79327</v>
+        <v>92281</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14781,21 +14793,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14805,10 +14817,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>689929</v>
+        <v>689506</v>
       </c>
       <c r="R137" t="n">
-        <v>7098189</v>
+        <v>7098051</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14835,12 +14847,12 @@
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>2015-05-18</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2015-10-30</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14851,33 +14863,27 @@
       </c>
       <c r="AG137" t="b">
         <v>0</v>
-      </c>
-      <c r="AI137" t="inlineStr">
-        <is>
-          <t>barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AO137" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
       </c>
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY137" t="inlineStr"/>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY137" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>56825835</v>
+        <v>56825832</v>
       </c>
       <c r="B138" t="n">
         <v>79327</v>
@@ -14912,10 +14918,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>689807</v>
+        <v>689929</v>
       </c>
       <c r="R138" t="n">
-        <v>7098230</v>
+        <v>7098189</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14984,7 +14990,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>56825838</v>
+        <v>56825835</v>
       </c>
       <c r="B139" t="n">
         <v>79327</v>
@@ -15019,10 +15025,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>689750</v>
+        <v>689807</v>
       </c>
       <c r="R139" t="n">
-        <v>7098282</v>
+        <v>7098230</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15073,7 +15079,7 @@
       </c>
       <c r="AO139" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AT139" t="inlineStr"/>
@@ -15091,7 +15097,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>56825843</v>
+        <v>56825838</v>
       </c>
       <c r="B140" t="n">
         <v>79327</v>
@@ -15126,10 +15132,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>689480</v>
+        <v>689750</v>
       </c>
       <c r="R140" t="n">
-        <v>7098098</v>
+        <v>7098282</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15180,7 +15186,7 @@
       </c>
       <c r="AO140" t="inlineStr">
         <is>
-          <t>gammal gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AT140" t="inlineStr"/>
@@ -15198,32 +15204,32 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>56825836</v>
+        <v>56825843</v>
       </c>
       <c r="B141" t="n">
-        <v>78730</v>
+        <v>79327</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15233,10 +15239,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>689763</v>
+        <v>689480</v>
       </c>
       <c r="R141" t="n">
-        <v>7098277</v>
+        <v>7098098</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15287,7 +15293,7 @@
       </c>
       <c r="AO141" t="inlineStr">
         <is>
-          <t>silverstubbe tall</t>
+          <t>gammal gran</t>
         </is>
       </c>
       <c r="AT141" t="inlineStr"/>
@@ -15305,10 +15311,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>126909285</v>
+        <v>56825836</v>
       </c>
       <c r="B142" t="n">
-        <v>79946</v>
+        <v>78730</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15316,34 +15322,34 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Rislidmyran, Rislidmyran, Ång</t>
+          <t>Rislidtjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>689571</v>
+        <v>689763</v>
       </c>
       <c r="R142" t="n">
-        <v>7098027</v>
+        <v>7098277</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15370,22 +15376,12 @@
       </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="Z142" t="inlineStr">
-        <is>
-          <t>15:11</t>
+          <t>2015-05-18</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB142" t="inlineStr">
-        <is>
-          <t>15:11</t>
+          <t>2015-10-30</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15396,27 +15392,33 @@
       </c>
       <c r="AG142" t="b">
         <v>0</v>
+      </c>
+      <c r="AI142" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO142" t="inlineStr">
+        <is>
+          <t>silverstubbe tall</t>
+        </is>
       </c>
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Eleonor Johansson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Eleonor Johansson, Lotta Ihse, Isac Enetjärn, Fredrik Wilde, Malin Löfgren, Emil Lindgren, Hedda Bring</t>
-        </is>
-      </c>
-      <c r="AY142" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>126917530</v>
+        <v>126909285</v>
       </c>
       <c r="B143" t="n">
         <v>79946</v>
@@ -15447,14 +15449,14 @@
       <c r="I143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Rislidtjärnarna, Ång</t>
+          <t>Rislidmyran, Rislidmyran, Ång</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>689577</v>
+        <v>689571</v>
       </c>
       <c r="R143" t="n">
-        <v>7098004</v>
+        <v>7098027</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15484,9 +15486,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z143" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
       <c r="AA143" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB143" t="inlineStr">
+        <is>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15501,12 +15513,12 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Eleonor Johansson</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Eleonor Johansson, Lotta Ihse, Isac Enetjärn, Fredrik Wilde, Malin Löfgren, Emil Lindgren, Hedda Bring</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr">
@@ -15517,10 +15529,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>56825840</v>
+        <v>126917530</v>
       </c>
       <c r="B144" t="n">
-        <v>80432</v>
+        <v>79946</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15528,21 +15540,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15552,10 +15564,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>689470</v>
+        <v>689577</v>
       </c>
       <c r="R144" t="n">
-        <v>7098090</v>
+        <v>7098004</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15582,12 +15594,12 @@
       </c>
       <c r="Y144" t="inlineStr">
         <is>
-          <t>2015-05-18</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2015-10-30</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15598,58 +15610,52 @@
       </c>
       <c r="AG144" t="b">
         <v>0</v>
-      </c>
-      <c r="AI144" t="inlineStr">
-        <is>
-          <t>barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AO144" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
       </c>
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY144" t="inlineStr"/>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY144" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>56825841</v>
+        <v>56825840</v>
       </c>
       <c r="B145" t="n">
-        <v>80467</v>
+        <v>80432</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15731,7 +15737,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>126917578</v>
+        <v>56825841</v>
       </c>
       <c r="B146" t="n">
         <v>80467</v>
@@ -15766,10 +15772,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>689471</v>
+        <v>689470</v>
       </c>
       <c r="R146" t="n">
-        <v>7098101</v>
+        <v>7098090</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15796,12 +15802,12 @@
       </c>
       <c r="Y146" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2015-05-18</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2015-10-30</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15812,30 +15818,36 @@
       </c>
       <c r="AG146" t="b">
         <v>0</v>
+      </c>
+      <c r="AI146" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO146" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
       </c>
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
-        </is>
-      </c>
-      <c r="AY146" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>126917540</v>
+        <v>126917578</v>
       </c>
       <c r="B147" t="n">
-        <v>57950</v>
+        <v>80467</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15843,38 +15855,34 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>100049</v>
+        <v>6463</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
-      <c r="K147" t="inlineStr"/>
-      <c r="L147" t="inlineStr"/>
-      <c r="M147" t="inlineStr"/>
-      <c r="N147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
           <t>Rislidtjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>689546</v>
+        <v>689471</v>
       </c>
       <c r="R147" t="n">
-        <v>7098019</v>
+        <v>7098101</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15907,11 +15915,6 @@
       <c r="AA147" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AC147" t="inlineStr">
-        <is>
-          <t>Ädre spår</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -15942,10 +15945,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>126909036</v>
+        <v>126917540</v>
       </c>
       <c r="B148" t="n">
-        <v>99035</v>
+        <v>57950</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15953,34 +15956,38 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>219790</v>
+        <v>100049</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
+      <c r="K148" t="inlineStr"/>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" t="inlineStr"/>
+      <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Rislidmyran, Rislidmyran, Ång</t>
+          <t>Rislidtjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>689499</v>
+        <v>689546</v>
       </c>
       <c r="R148" t="n">
-        <v>7098043</v>
+        <v>7098019</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16010,19 +16017,14 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z148" t="inlineStr">
-        <is>
-          <t>14:48</t>
-        </is>
-      </c>
       <c r="AA148" t="inlineStr">
         <is>
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AB148" t="inlineStr">
-        <is>
-          <t>14:48</t>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>Ädre spår</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16037,12 +16039,12 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Eleonor Johansson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Eleonor Johansson, Lotta Ihse, Isac Enetjärn, Fredrik Wilde, Malin Löfgren, Emil Lindgren, Hedda Bring</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr">
@@ -16053,49 +16055,45 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>126908916</v>
+        <v>126909036</v>
       </c>
       <c r="B149" t="n">
-        <v>99118</v>
+        <v>99035</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
           <t>Rislidmyran, Rislidmyran, Ång</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>689502</v>
+        <v>689499</v>
       </c>
       <c r="R149" t="n">
-        <v>7098047</v>
+        <v>7098043</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16127,7 +16125,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -16137,7 +16135,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16168,45 +16166,49 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>126915424</v>
+        <v>126908916</v>
       </c>
       <c r="B150" t="n">
-        <v>79085</v>
+        <v>99118</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Rislidtjärnarna, Ång</t>
+          <t>Rislidmyran, Rislidmyran, Ång</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>689574</v>
+        <v>689502</v>
       </c>
       <c r="R150" t="n">
-        <v>7098012</v>
+        <v>7098047</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16236,9 +16238,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z150" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
       <c r="AA150" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB150" t="inlineStr">
+        <is>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16253,12 +16265,12 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Eleonor Johansson</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Hedda Bring, Eleonor Johansson, Emil Lindgren, Fredrik Wilde, Isac Enetjärn, Lotta Ihse, Malin Löfgren, Eleonor Johansson, Emil Lindgren, Fredrik Wilde, Isac Enetjärn, Lotta Ihse, Malin Löfgren</t>
+          <t>Eleonor Johansson, Lotta Ihse, Isac Enetjärn, Fredrik Wilde, Malin Löfgren, Emil Lindgren, Hedda Bring</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr">
@@ -16269,7 +16281,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>126917547</v>
+        <v>126915424</v>
       </c>
       <c r="B151" t="n">
         <v>79085</v>
@@ -16304,10 +16316,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>689504</v>
+        <v>689574</v>
       </c>
       <c r="R151" t="n">
-        <v>7098070</v>
+        <v>7098012</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16354,12 +16366,12 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Hedda Bring, Eleonor Johansson, Emil Lindgren, Fredrik Wilde, Isac Enetjärn, Lotta Ihse, Malin Löfgren, Eleonor Johansson, Emil Lindgren, Fredrik Wilde, Isac Enetjärn, Lotta Ihse, Malin Löfgren</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr">
@@ -16370,10 +16382,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>56825816</v>
+        <v>126917547</v>
       </c>
       <c r="B152" t="n">
-        <v>92208</v>
+        <v>79085</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16381,21 +16393,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>658</v>
+        <v>228912</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16405,10 +16417,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>690185</v>
+        <v>689504</v>
       </c>
       <c r="R152" t="n">
-        <v>7098034</v>
+        <v>7098070</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16435,12 +16447,12 @@
       </c>
       <c r="Y152" t="inlineStr">
         <is>
-          <t>2015-05-18</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>2015-10-30</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16451,36 +16463,30 @@
       </c>
       <c r="AG152" t="b">
         <v>0</v>
-      </c>
-      <c r="AI152" t="inlineStr">
-        <is>
-          <t>barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AO152" t="inlineStr">
-        <is>
-          <t>granlåga</t>
-        </is>
       </c>
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY152" t="inlineStr"/>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY152" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>56825820</v>
+        <v>56825816</v>
       </c>
       <c r="B153" t="n">
-        <v>81312</v>
+        <v>92208</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16488,21 +16494,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>1049</v>
+        <v>658</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16512,10 +16518,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>690121</v>
+        <v>690185</v>
       </c>
       <c r="R153" t="n">
-        <v>7098032</v>
+        <v>7098034</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16566,7 +16572,7 @@
       </c>
       <c r="AO153" t="inlineStr">
         <is>
-          <t>högstubbe gran</t>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AT153" t="inlineStr"/>
@@ -16584,10 +16590,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>56825830</v>
+        <v>56825820</v>
       </c>
       <c r="B154" t="n">
-        <v>91905</v>
+        <v>81312</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16595,21 +16601,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>1108</v>
+        <v>1049</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16619,10 +16625,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>689974</v>
+        <v>690121</v>
       </c>
       <c r="R154" t="n">
-        <v>7098206</v>
+        <v>7098032</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16673,7 +16679,7 @@
       </c>
       <c r="AO154" t="inlineStr">
         <is>
-          <t>torrgran</t>
+          <t>högstubbe gran</t>
         </is>
       </c>
       <c r="AT154" t="inlineStr"/>
@@ -16691,10 +16697,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>56825806</v>
+        <v>56825830</v>
       </c>
       <c r="B155" t="n">
-        <v>91909</v>
+        <v>91905</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16702,21 +16708,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16726,10 +16732,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>690295</v>
+        <v>689974</v>
       </c>
       <c r="R155" t="n">
-        <v>7097931</v>
+        <v>7098206</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16780,7 +16786,7 @@
       </c>
       <c r="AO155" t="inlineStr">
         <is>
-          <t>granlåga</t>
+          <t>torrgran</t>
         </is>
       </c>
       <c r="AT155" t="inlineStr"/>
@@ -16798,7 +16804,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>56825809</v>
+        <v>56825806</v>
       </c>
       <c r="B156" t="n">
         <v>91909</v>
@@ -16833,10 +16839,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>690275</v>
+        <v>690295</v>
       </c>
       <c r="R156" t="n">
-        <v>7097957</v>
+        <v>7097931</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16905,7 +16911,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>56825814</v>
+        <v>56825809</v>
       </c>
       <c r="B157" t="n">
         <v>91909</v>
@@ -16940,10 +16946,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>690195</v>
+        <v>690275</v>
       </c>
       <c r="R157" t="n">
-        <v>7098012</v>
+        <v>7097957</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17012,7 +17018,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>56825815</v>
+        <v>56825814</v>
       </c>
       <c r="B158" t="n">
         <v>91909</v>
@@ -17047,10 +17053,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>690185</v>
+        <v>690195</v>
       </c>
       <c r="R158" t="n">
-        <v>7098034</v>
+        <v>7098012</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17119,10 +17125,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>56825805</v>
+        <v>56825815</v>
       </c>
       <c r="B159" t="n">
-        <v>83173</v>
+        <v>91909</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17130,21 +17136,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -17154,10 +17160,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>690282</v>
+        <v>690185</v>
       </c>
       <c r="R159" t="n">
-        <v>7097946</v>
+        <v>7098034</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17208,7 +17214,7 @@
       </c>
       <c r="AO159" t="inlineStr">
         <is>
-          <t>gammal gran</t>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AT159" t="inlineStr"/>
@@ -17226,7 +17232,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>56825807</v>
+        <v>56825805</v>
       </c>
       <c r="B160" t="n">
         <v>83173</v>
@@ -17261,10 +17267,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>690289</v>
+        <v>690282</v>
       </c>
       <c r="R160" t="n">
-        <v>7097937</v>
+        <v>7097946</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17333,7 +17339,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>56825810</v>
+        <v>56825807</v>
       </c>
       <c r="B161" t="n">
         <v>83173</v>
@@ -17368,10 +17374,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>690220</v>
+        <v>690289</v>
       </c>
       <c r="R161" t="n">
-        <v>7097986</v>
+        <v>7097937</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17440,7 +17446,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>56825811</v>
+        <v>56825810</v>
       </c>
       <c r="B162" t="n">
         <v>83173</v>
@@ -17475,10 +17481,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>690200</v>
+        <v>690220</v>
       </c>
       <c r="R162" t="n">
-        <v>7097985</v>
+        <v>7097986</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17547,7 +17553,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>56825812</v>
+        <v>56825811</v>
       </c>
       <c r="B163" t="n">
         <v>83173</v>
@@ -17582,10 +17588,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>690202</v>
+        <v>690200</v>
       </c>
       <c r="R163" t="n">
-        <v>7098003</v>
+        <v>7097985</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17654,7 +17660,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>56825813</v>
+        <v>56825812</v>
       </c>
       <c r="B164" t="n">
         <v>83173</v>
@@ -17689,10 +17695,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>690203</v>
+        <v>690202</v>
       </c>
       <c r="R164" t="n">
-        <v>7098001</v>
+        <v>7098003</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17761,7 +17767,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>56825826</v>
+        <v>56825813</v>
       </c>
       <c r="B165" t="n">
         <v>83173</v>
@@ -17796,10 +17802,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>690072</v>
+        <v>690203</v>
       </c>
       <c r="R165" t="n">
-        <v>7098095</v>
+        <v>7098001</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17868,7 +17874,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>56825828</v>
+        <v>56825826</v>
       </c>
       <c r="B166" t="n">
         <v>83173</v>
@@ -17903,10 +17909,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>690073</v>
+        <v>690072</v>
       </c>
       <c r="R166" t="n">
-        <v>7098117</v>
+        <v>7098095</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17975,32 +17981,32 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>56825802</v>
+        <v>56825828</v>
       </c>
       <c r="B167" t="n">
-        <v>91872</v>
+        <v>83173</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -18010,10 +18016,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>690359</v>
+        <v>690073</v>
       </c>
       <c r="R167" t="n">
-        <v>7097938</v>
+        <v>7098117</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18064,7 +18070,7 @@
       </c>
       <c r="AO167" t="inlineStr">
         <is>
-          <t>granlåga</t>
+          <t>gammal gran</t>
         </is>
       </c>
       <c r="AT167" t="inlineStr"/>
@@ -18082,7 +18088,7 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>56825808</v>
+        <v>56825802</v>
       </c>
       <c r="B168" t="n">
         <v>91872</v>
@@ -18117,10 +18123,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>690275</v>
+        <v>690359</v>
       </c>
       <c r="R168" t="n">
-        <v>7097957</v>
+        <v>7097938</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18189,7 +18195,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>56825817</v>
+        <v>56825808</v>
       </c>
       <c r="B169" t="n">
         <v>91872</v>
@@ -18224,10 +18230,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>690185</v>
+        <v>690275</v>
       </c>
       <c r="R169" t="n">
-        <v>7098034</v>
+        <v>7097957</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18296,32 +18302,32 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>56825803</v>
+        <v>56825817</v>
       </c>
       <c r="B170" t="n">
-        <v>79327</v>
+        <v>91872</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -18331,10 +18337,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>690345</v>
+        <v>690185</v>
       </c>
       <c r="R170" t="n">
-        <v>7097944</v>
+        <v>7098034</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18385,7 +18391,7 @@
       </c>
       <c r="AO170" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AT170" t="inlineStr"/>
@@ -18403,7 +18409,7 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>56825819</v>
+        <v>56825803</v>
       </c>
       <c r="B171" t="n">
         <v>79327</v>
@@ -18438,10 +18444,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>690152</v>
+        <v>690345</v>
       </c>
       <c r="R171" t="n">
-        <v>7098021</v>
+        <v>7097944</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18510,7 +18516,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>56825827</v>
+        <v>56825819</v>
       </c>
       <c r="B172" t="n">
         <v>79327</v>
@@ -18545,10 +18551,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>690069</v>
+        <v>690152</v>
       </c>
       <c r="R172" t="n">
-        <v>7098107</v>
+        <v>7098021</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18617,7 +18623,7 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>56825829</v>
+        <v>56825827</v>
       </c>
       <c r="B173" t="n">
         <v>79327</v>
@@ -18652,10 +18658,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>690002</v>
+        <v>690069</v>
       </c>
       <c r="R173" t="n">
-        <v>7098171</v>
+        <v>7098107</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18724,7 +18730,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>56825855</v>
+        <v>56825829</v>
       </c>
       <c r="B174" t="n">
         <v>79327</v>
@@ -18759,10 +18765,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>690016</v>
+        <v>690002</v>
       </c>
       <c r="R174" t="n">
-        <v>7098001</v>
+        <v>7098171</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18831,7 +18837,7 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>56825859</v>
+        <v>56825855</v>
       </c>
       <c r="B175" t="n">
         <v>79327</v>
@@ -18866,10 +18872,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>690179</v>
+        <v>690016</v>
       </c>
       <c r="R175" t="n">
-        <v>7097969</v>
+        <v>7098001</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18938,32 +18944,32 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>56825824</v>
+        <v>56825859</v>
       </c>
       <c r="B176" t="n">
-        <v>80336</v>
+        <v>79327</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -18973,10 +18979,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>690115</v>
+        <v>690179</v>
       </c>
       <c r="R176" t="n">
-        <v>7098048</v>
+        <v>7097969</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19027,7 +19033,7 @@
       </c>
       <c r="AO176" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AT176" t="inlineStr"/>
@@ -19045,32 +19051,32 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>56825821</v>
+        <v>56825824</v>
       </c>
       <c r="B177" t="n">
-        <v>80432</v>
+        <v>80336</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -19080,10 +19086,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>690103</v>
+        <v>690115</v>
       </c>
       <c r="R177" t="n">
-        <v>7098031</v>
+        <v>7098048</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19134,7 +19140,7 @@
       </c>
       <c r="AO177" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AT177" t="inlineStr"/>
@@ -19152,32 +19158,32 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>56825822</v>
+        <v>56825821</v>
       </c>
       <c r="B178" t="n">
-        <v>80468</v>
+        <v>80432</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -19259,32 +19265,32 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>56825823</v>
+        <v>56825822</v>
       </c>
       <c r="B179" t="n">
-        <v>57953</v>
+        <v>80468</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -19344,6 +19350,11 @@
       <c r="AI179" t="inlineStr">
         <is>
           <t>barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO179" t="inlineStr">
+        <is>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AT179" t="inlineStr"/>
@@ -19361,32 +19372,32 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>56825867</v>
+        <v>56825823</v>
       </c>
       <c r="B180" t="n">
-        <v>99118</v>
+        <v>57953</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -19396,10 +19407,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>690415</v>
+        <v>690103</v>
       </c>
       <c r="R180" t="n">
-        <v>7097829</v>
+        <v>7098031</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19463,32 +19474,32 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>56825871</v>
+        <v>56825867</v>
       </c>
       <c r="B181" t="n">
-        <v>83299</v>
+        <v>99118</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -19498,10 +19509,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>690570</v>
+        <v>690415</v>
       </c>
       <c r="R181" t="n">
-        <v>7097685</v>
+        <v>7097829</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19548,11 +19559,6 @@
       <c r="AI181" t="inlineStr">
         <is>
           <t>barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AO181" t="inlineStr">
-        <is>
-          <t>björkstubbe</t>
         </is>
       </c>
       <c r="AT181" t="inlineStr"/>
@@ -19570,32 +19576,32 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>56825876</v>
+        <v>56825871</v>
       </c>
       <c r="B182" t="n">
-        <v>96338</v>
+        <v>83299</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>2809</v>
+        <v>308</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -19605,10 +19611,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>690596</v>
+        <v>690570</v>
       </c>
       <c r="R182" t="n">
-        <v>7097698</v>
+        <v>7097685</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19655,6 +19661,11 @@
       <c r="AI182" t="inlineStr">
         <is>
           <t>barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO182" t="inlineStr">
+        <is>
+          <t>björkstubbe</t>
         </is>
       </c>
       <c r="AT182" t="inlineStr"/>
@@ -19672,32 +19683,32 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>56825875</v>
+        <v>56825876</v>
       </c>
       <c r="B183" t="n">
-        <v>79327</v>
+        <v>96338</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -19707,10 +19718,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>690592</v>
+        <v>690596</v>
       </c>
       <c r="R183" t="n">
-        <v>7097685</v>
+        <v>7097698</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19757,11 +19768,6 @@
       <c r="AI183" t="inlineStr">
         <is>
           <t>barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AO183" t="inlineStr">
-        <is>
-          <t>gran</t>
         </is>
       </c>
       <c r="AT183" t="inlineStr"/>
@@ -19779,32 +19785,32 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>56825868</v>
+        <v>56825875</v>
       </c>
       <c r="B184" t="n">
-        <v>80432</v>
+        <v>79327</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -19814,10 +19820,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>690537</v>
+        <v>690592</v>
       </c>
       <c r="R184" t="n">
-        <v>7097733</v>
+        <v>7097685</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19868,7 +19874,7 @@
       </c>
       <c r="AO184" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AT184" t="inlineStr"/>
@@ -19886,7 +19892,7 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>56825870</v>
+        <v>56825868</v>
       </c>
       <c r="B185" t="n">
         <v>80432</v>
@@ -19921,10 +19927,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>690562</v>
+        <v>690537</v>
       </c>
       <c r="R185" t="n">
-        <v>7097708</v>
+        <v>7097733</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19993,7 +19999,7 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>56825872</v>
+        <v>56825870</v>
       </c>
       <c r="B186" t="n">
         <v>80432</v>
@@ -20028,10 +20034,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>690574</v>
+        <v>690562</v>
       </c>
       <c r="R186" t="n">
-        <v>7097671</v>
+        <v>7097708</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20100,7 +20106,7 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>56825878</v>
+        <v>56825872</v>
       </c>
       <c r="B187" t="n">
         <v>80432</v>
@@ -20135,10 +20141,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>690641</v>
+        <v>690574</v>
       </c>
       <c r="R187" t="n">
-        <v>7097580</v>
+        <v>7097671</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -20189,7 +20195,7 @@
       </c>
       <c r="AO187" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AT187" t="inlineStr"/>
@@ -20207,32 +20213,32 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>56825869</v>
+        <v>56825878</v>
       </c>
       <c r="B188" t="n">
-        <v>80461</v>
+        <v>80432</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -20242,10 +20248,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>690537</v>
+        <v>690641</v>
       </c>
       <c r="R188" t="n">
-        <v>7097733</v>
+        <v>7097580</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20296,7 +20302,7 @@
       </c>
       <c r="AO188" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AT188" t="inlineStr"/>
@@ -20314,7 +20320,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>56825873</v>
+        <v>56825869</v>
       </c>
       <c r="B189" t="n">
         <v>80461</v>
@@ -20349,10 +20355,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>690574</v>
+        <v>690537</v>
       </c>
       <c r="R189" t="n">
-        <v>7097671</v>
+        <v>7097733</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20421,10 +20427,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>56825874</v>
+        <v>56825873</v>
       </c>
       <c r="B190" t="n">
-        <v>80398</v>
+        <v>80461</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -20432,21 +20438,21 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>229748</v>
+        <v>6462</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -20525,6 +20531,113 @@
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>56825874</v>
+      </c>
+      <c r="B191" t="n">
+        <v>80398</v>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E191" t="n">
+        <v>229748</v>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>Gytterlav</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>Protopannaria pezizoides</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr"/>
+      <c r="P191" t="inlineStr">
+        <is>
+          <t>Rislidtjärnarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q191" t="n">
+        <v>690574</v>
+      </c>
+      <c r="R191" t="n">
+        <v>7097671</v>
+      </c>
+      <c r="S191" t="n">
+        <v>10</v>
+      </c>
+      <c r="T191" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U191" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V191" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W191" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y191" t="inlineStr">
+        <is>
+          <t>2015-05-18</t>
+        </is>
+      </c>
+      <c r="AA191" t="inlineStr">
+        <is>
+          <t>2015-10-30</t>
+        </is>
+      </c>
+      <c r="AD191" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE191" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG191" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI191" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO191" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AT191" t="inlineStr"/>
+      <c r="AW191" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX191" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY191" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
